--- a/artfynd/A 53728-2025 artfynd.xlsx
+++ b/artfynd/A 53728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80852575</v>
+        <v>104684909</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Markbygden, Nb</t>
+          <t>Håltjärnen, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753076.1218312259</v>
+        <v>753021</v>
       </c>
       <c r="R2" t="n">
-        <v>7272249.973457895</v>
+        <v>7272395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80852576</v>
+        <v>104684910</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Markbygden, Nb</t>
+          <t>Håltjärnen, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753038.9117131056</v>
+        <v>752991</v>
       </c>
       <c r="R3" t="n">
-        <v>7272230.866789589</v>
+        <v>7272268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,62 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104684909</v>
+        <v>80852577</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Håltjärnen, Nb</t>
+          <t>Markbygden, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753021.3020991336</v>
+        <v>753024</v>
       </c>
       <c r="R4" t="n">
-        <v>7272394.666035392</v>
+        <v>7272228</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104684910</v>
+        <v>104684642</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Håltjärnen, Nb</t>
+          <t>Stavaliden, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752990.9137116168</v>
+        <v>753086</v>
       </c>
       <c r="R5" t="n">
-        <v>7272268.438468937</v>
+        <v>7272459</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1126,12 +1066,7 @@
         <v>104684857</v>
       </c>
       <c r="B6" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753019.4623302362</v>
+        <v>753019</v>
       </c>
       <c r="R6" t="n">
-        <v>7272396.593283123</v>
+        <v>7272396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104684642</v>
+        <v>80852576</v>
       </c>
       <c r="B7" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stavaliden, Nb</t>
+          <t>Markbygden, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753085.4535775924</v>
+        <v>753039</v>
       </c>
       <c r="R7" t="n">
-        <v>7272459.537770537</v>
+        <v>7272231</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,15 +1245,112 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Aron Dynesius</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>80852575</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Markbygden, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>753076</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7272250</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53728-2025 artfynd.xlsx
+++ b/artfynd/A 53728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104684909</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104684910</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80852577</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104684642</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104684857</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80852576</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,8 +1386,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80852575</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>